--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
@@ -241,7 +241,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -268,17 +268,17 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限控制</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -328,7 +328,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -355,12 +355,12 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
@@ -413,7 +413,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -440,12 +440,12 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
@@ -499,7 +499,7 @@
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -526,12 +526,12 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
@@ -585,7 +585,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -612,12 +612,12 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
@@ -671,7 +671,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -698,12 +698,12 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
@@ -759,7 +759,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -786,17 +786,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑规则</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="L9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M9" t="inlineStr" s="2">
@@ -874,12 +874,12 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
@@ -934,7 +934,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -961,17 +961,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑弹窗</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1047,12 +1047,12 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1133,17 +1133,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">等级行维护</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1220,17 +1220,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">等级行维护</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1305,12 +1305,12 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1393,12 +1393,12 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1479,12 +1479,12 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1565,17 +1565,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">字段校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1650,17 +1650,17 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">字段校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1736,17 +1736,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">字段校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M20" t="inlineStr" s="2">
@@ -1822,12 +1822,12 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -1908,17 +1908,17 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">区间校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -1994,17 +1994,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">区间校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2080,17 +2080,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">区间校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2166,17 +2166,17 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">区间校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2252,12 +2252,12 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2338,12 +2338,12 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
@@ -2425,12 +2425,12 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
@@ -2512,12 +2512,12 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2600,17 +2600,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2688,17 +2688,17 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -2776,12 +2776,12 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -2863,12 +2863,12 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量规则配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
@@ -202,7 +202,7 @@
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
@@ -241,7 +241,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -288,7 +288,7 @@
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
@@ -499,7 +499,7 @@
       </c>
       <c r="L5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M5" t="inlineStr" s="2">
@@ -546,7 +546,7 @@
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
@@ -585,7 +585,7 @@
       </c>
       <c r="L6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M6" t="inlineStr" s="2">
@@ -671,7 +671,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -806,7 +806,7 @@
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
@@ -894,7 +894,7 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -934,7 +934,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="L17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M17" t="inlineStr" s="2">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="L19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M19" t="inlineStr" s="2">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M20" t="inlineStr" s="2">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有质量规则配置编辑权限和审计追踪查看权限
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有质量规则配置编辑权限和审计追踪菜单权限
 2. 已修改并保存 PPK 等级规则</t>
         </is>
       </c>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/quality_rule_config_testcases.xlsx
@@ -2215,7 +2215,7 @@
         <is>
           <t xml:space="preserve">1. 最低等级最小值为空表示负无穷，最高等级最大值为空表示正无穷
 2. 系统允许保存覆盖负无穷到正无穷的合法规则
-3. 预览中最低等级和最高等级范围展示符合无穷边界规则</t>
+3. 预览中最低等级范围展示为无下限到 0.67，最高等级范围展示为 2.0 到无上限</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2467,7 +2467,7 @@
       <c r="I28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按操作模块质量规则配置筛选最新编辑记录
+2. 在操作模块筛选项选择质量规则配置，查看最新编辑记录
 3. 打开审计追踪详情</t>
         </is>
       </c>
@@ -2561,8 +2561,8 @@
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 过程能力（正态）按最新 CPK 规则判定 CPK 等级
-2. 过程能力（正态）按最新 PPK 规则判定 PPK 等级
+          <t xml:space="preserve">1. 过程能力（正态）使用最新 CPK 等级配置判定 CPK 等级
+2. 过程能力（正态）使用最新 PPK 等级配置判定 PPK 等级
 3. 分析结果中的等级名称和描述说明与能力分析等级配置一致</t>
         </is>
       </c>
@@ -2649,8 +2649,8 @@
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 过程能力（非正态）中非参数法按最新 CPK 规则判定等级
-2. 过程能力（非正态）中 WEIBULL 拟合按最新 PPK 规则判定等级
+          <t xml:space="preserve">1. 过程能力（非正态）中非参数法使用最新 CPK 等级配置判定等级
+2. 过程能力（非正态）中 WEIBULL 拟合使用最新 PPK 等级配置判定等级
 3. 不使用修改前的固定等级标准生成结论</t>
         </is>
       </c>
@@ -2738,8 +2738,8 @@
       <c r="J31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已生成的历史分析结果 R 不被规则变更静默改写
-2. 重新分析后的新结果按最新规则生成等级结论
-3. 新旧结果可区分分析时间和使用规则版本或审计记录</t>
+2. 重新分析后的新结果使用最新能力分析等级配置生成等级结论
+3. 新旧结果可区分分析时间和使用配置版本或审计记录</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
